--- a/data/nzd0014/nzd0014.xlsx
+++ b/data/nzd0014/nzd0014.xlsx
@@ -4420,7 +4420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B280"/>
+  <dimension ref="A1:B281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7223,6 +7223,16 @@
       </c>
       <c r="B280" t="n">
         <v>-0.13</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>0.99</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0014/nzd0014.xlsx
+++ b/data/nzd0014/nzd0014.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D223"/>
+  <dimension ref="A1:D225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4406,6 +4406,42 @@
       <c r="D223" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>374.13</v>
+      </c>
+      <c r="C224" t="n">
+        <v>366.73</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>371.98</v>
+      </c>
+      <c r="C225" t="n">
+        <v>382.38</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B281"/>
+  <dimension ref="A1:B283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7233,6 +7269,26 @@
       </c>
       <c r="B281" t="n">
         <v>0.99</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>0.91</v>
       </c>
     </row>
   </sheetData>
@@ -7401,28 +7457,28 @@
         <v>0.1292</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01429542000527944</v>
+        <v>-0.01321481242032905</v>
       </c>
       <c r="J2" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="K2" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004735536753751601</v>
+        <v>0.0004122735664101596</v>
       </c>
       <c r="M2" t="n">
-        <v>4.216856503801674</v>
+        <v>4.188421896644076</v>
       </c>
       <c r="N2" t="n">
-        <v>26.58965344144351</v>
+        <v>26.36634118027184</v>
       </c>
       <c r="O2" t="n">
-        <v>5.156515629903928</v>
+        <v>5.134816567344138</v>
       </c>
       <c r="P2" t="n">
-        <v>372.7701672161248</v>
+        <v>372.7599090973861</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -7483,28 +7539,28 @@
         <v>0.0108</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.614403934520937</v>
+        <v>-1.654116612801297</v>
       </c>
       <c r="J3" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="K3" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1500859319058779</v>
+        <v>0.1583425068960347</v>
       </c>
       <c r="M3" t="n">
-        <v>24.47594634236891</v>
+        <v>24.40440359758296</v>
       </c>
       <c r="N3" t="n">
-        <v>860.6019891405891</v>
+        <v>857.2293978972548</v>
       </c>
       <c r="O3" t="n">
-        <v>29.33601863137854</v>
+        <v>29.27848011590176</v>
       </c>
       <c r="P3" t="n">
-        <v>438.8042550080158</v>
+        <v>439.2016838052655</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -7542,7 +7598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D223"/>
+  <dimension ref="A1:D225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12371,6 +12427,50 @@
         </is>
       </c>
     </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>-34.72455460204407,173.0925149111753</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>-34.72527685729475,173.09263469840928</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>-34.724558965178055,173.0924920307363</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>-34.72524509754196,173.0928012480763</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0014/nzd0014.xlsx
+++ b/data/nzd0014/nzd0014.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D225"/>
+  <dimension ref="A1:D227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4437,11 +4437,47 @@
         <v>371.98</v>
       </c>
       <c r="C225" t="n">
-        <v>382.38</v>
+        <v>366.73</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>369.76</v>
+      </c>
+      <c r="C226" t="n">
+        <v>373.92</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:17:31+00:00</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>370.09</v>
+      </c>
+      <c r="C227" t="n">
+        <v>373.92</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -4456,7 +4492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B283"/>
+  <dimension ref="A1:B285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7289,6 +7325,26 @@
       </c>
       <c r="B283" t="n">
         <v>0.91</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -7457,28 +7513,28 @@
         <v>0.1292</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01321481242032905</v>
+        <v>-0.01723000700129779</v>
       </c>
       <c r="J2" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="K2" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004122735664101596</v>
+        <v>0.0007126245294988287</v>
       </c>
       <c r="M2" t="n">
-        <v>4.188421896644076</v>
+        <v>4.174459248251346</v>
       </c>
       <c r="N2" t="n">
-        <v>26.36634118027184</v>
+        <v>26.18621861840871</v>
       </c>
       <c r="O2" t="n">
-        <v>5.134816567344138</v>
+        <v>5.11724717190881</v>
       </c>
       <c r="P2" t="n">
-        <v>372.7599090973861</v>
+        <v>372.7983849760686</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -7539,28 +7595,28 @@
         <v>0.0108</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.654116612801297</v>
+        <v>-1.706667678440352</v>
       </c>
       <c r="J3" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="K3" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1583425068960347</v>
+        <v>0.1685064274078247</v>
       </c>
       <c r="M3" t="n">
-        <v>24.40440359758296</v>
+        <v>24.38830157447666</v>
       </c>
       <c r="N3" t="n">
-        <v>857.2293978972548</v>
+        <v>856.2806672292973</v>
       </c>
       <c r="O3" t="n">
-        <v>29.27848011590176</v>
+        <v>29.26227378775097</v>
       </c>
       <c r="P3" t="n">
-        <v>439.2016838052655</v>
+        <v>439.7309617899032</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -7598,7 +7654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D225"/>
+  <dimension ref="A1:D227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12462,12 +12518,56 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>-34.72524509754196,173.0928012480763</t>
+          <t>-34.72527685729475,173.09263469840928</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>-34.72456347036306,173.09246840535033</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>-34.725262266101126,173.09271121549264</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:17:31+00:00</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>-34.72456280067369,173.0924719172322</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>-34.725262266101126,173.09271121549264</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0014/nzd0014.xlsx
+++ b/data/nzd0014/nzd0014.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D227"/>
+  <dimension ref="A1:D229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4476,6 +4476,42 @@
         <v>373.92</v>
       </c>
       <c r="D227" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>371.02</v>
+      </c>
+      <c r="C228" t="n">
+        <v>373.92</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>367.68</v>
+      </c>
+      <c r="C229" t="n">
+        <v>408.2</v>
+      </c>
+      <c r="D229" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -4492,7 +4528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B285"/>
+  <dimension ref="A1:B287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7345,6 +7381,26 @@
       </c>
       <c r="B285" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>0.78</v>
       </c>
     </row>
   </sheetData>
@@ -7513,28 +7569,28 @@
         <v>0.1292</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01723000700129779</v>
+        <v>-0.02198200431467962</v>
       </c>
       <c r="J2" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K2" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007126245294988287</v>
+        <v>0.001176542249101131</v>
       </c>
       <c r="M2" t="n">
-        <v>4.174459248251346</v>
+        <v>4.165098817293609</v>
       </c>
       <c r="N2" t="n">
-        <v>26.18621861840871</v>
+        <v>26.05722540906023</v>
       </c>
       <c r="O2" t="n">
-        <v>5.11724717190881</v>
+        <v>5.104627842366202</v>
       </c>
       <c r="P2" t="n">
-        <v>372.7983849760686</v>
+        <v>372.844164430003</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -7595,28 +7651,28 @@
         <v>0.0108</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.706667678440352</v>
+        <v>-1.712235971583521</v>
       </c>
       <c r="J3" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K3" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1685064274078247</v>
+        <v>0.1717581495515684</v>
       </c>
       <c r="M3" t="n">
-        <v>24.38830157447666</v>
+        <v>24.31259180673674</v>
       </c>
       <c r="N3" t="n">
-        <v>856.2806672292973</v>
+        <v>850.9866460983874</v>
       </c>
       <c r="O3" t="n">
-        <v>29.26227378775097</v>
+        <v>29.1716754078059</v>
       </c>
       <c r="P3" t="n">
-        <v>439.7309617899032</v>
+        <v>439.7869070116836</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -7654,7 +7710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D227"/>
+  <dimension ref="A1:D229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12571,6 +12627,50 @@
         </is>
       </c>
     </row>
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>-34.72456091336672,173.0924818143535</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>-34.725262266101126,173.09271121549264</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>-34.72456769143314,173.09244626985122</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>-34.72519269852561,173.09307602814204</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0014/nzd0014.xlsx
+++ b/data/nzd0014/nzd0014.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D229"/>
+  <dimension ref="A1:D231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4509,11 +4509,47 @@
         <v>367.68</v>
       </c>
       <c r="C229" t="n">
-        <v>408.2</v>
+        <v>378.91</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>367.81</v>
+      </c>
+      <c r="C230" t="n">
+        <v>369.43</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>367.74</v>
+      </c>
+      <c r="C231" t="n">
+        <v>362.64</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B287"/>
+  <dimension ref="A1:B289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7401,6 +7437,26 @@
       </c>
       <c r="B287" t="n">
         <v>0.78</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>-0.35</v>
       </c>
     </row>
   </sheetData>
@@ -7569,28 +7625,28 @@
         <v>0.1292</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02198200431467962</v>
+        <v>-0.02895566726187226</v>
       </c>
       <c r="J2" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K2" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001176542249101131</v>
+        <v>0.002063424250037915</v>
       </c>
       <c r="M2" t="n">
-        <v>4.165098817293609</v>
+        <v>4.168397970569581</v>
       </c>
       <c r="N2" t="n">
-        <v>26.05722540906023</v>
+        <v>26.0008235414741</v>
       </c>
       <c r="O2" t="n">
-        <v>5.104627842366202</v>
+        <v>5.099100267838837</v>
       </c>
       <c r="P2" t="n">
-        <v>372.844164430003</v>
+        <v>372.9115413583381</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -7651,28 +7707,28 @@
         <v>0.0108</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.712235971583521</v>
+        <v>-1.785928122320071</v>
       </c>
       <c r="J3" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K3" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1717581495515684</v>
+        <v>0.185728948364953</v>
       </c>
       <c r="M3" t="n">
-        <v>24.31259180673674</v>
+        <v>24.2467987579519</v>
       </c>
       <c r="N3" t="n">
-        <v>850.9866460983874</v>
+        <v>850.1146078242639</v>
       </c>
       <c r="O3" t="n">
-        <v>29.1716754078059</v>
+        <v>29.15672491594802</v>
       </c>
       <c r="P3" t="n">
-        <v>439.7869070116836</v>
+        <v>440.5360565683129</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -7710,7 +7766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D229"/>
+  <dimension ref="A1:D231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12662,12 +12718,56 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>-34.72519269852561,173.09307602814204</t>
+          <t>-34.7252521395004,173.09276431982252</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>-34.72456742761637,173.09244765331997</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>-34.72527137799263,173.0926634322268</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>-34.72456756967155,173.09244690837525</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>-34.72528515740989,173.09259117198957</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0014/nzd0014.xlsx
+++ b/data/nzd0014/nzd0014.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D231"/>
+  <dimension ref="A1:D232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4550,6 +4550,24 @@
       <c r="D231" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>369.66</v>
+      </c>
+      <c r="C232" t="n">
+        <v>360.63</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B289"/>
+  <dimension ref="A1:B290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7457,6 +7475,16 @@
       </c>
       <c r="B289" t="n">
         <v>-0.35</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>-0.24</v>
       </c>
     </row>
   </sheetData>
@@ -7625,28 +7653,28 @@
         <v>0.1292</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02895566726187226</v>
+        <v>-0.03087136516699724</v>
       </c>
       <c r="J2" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K2" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002063424250037915</v>
+        <v>0.002363529968639755</v>
       </c>
       <c r="M2" t="n">
-        <v>4.168397970569581</v>
+        <v>4.161234583327161</v>
       </c>
       <c r="N2" t="n">
-        <v>26.0008235414741</v>
+        <v>25.91448566543923</v>
       </c>
       <c r="O2" t="n">
-        <v>5.099100267838837</v>
+        <v>5.09062723693645</v>
       </c>
       <c r="P2" t="n">
-        <v>372.9115413583381</v>
+        <v>372.9301311465413</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -7707,28 +7735,28 @@
         <v>0.0108</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.785928122320071</v>
+        <v>-1.813457848889763</v>
       </c>
       <c r="J3" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K3" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L3" t="n">
-        <v>0.185728948364953</v>
+        <v>0.1910124236671908</v>
       </c>
       <c r="M3" t="n">
-        <v>24.2467987579519</v>
+        <v>24.2494275902066</v>
       </c>
       <c r="N3" t="n">
-        <v>850.1146078242639</v>
+        <v>850.8783331747925</v>
       </c>
       <c r="O3" t="n">
-        <v>29.15672491594802</v>
+        <v>29.16981887456267</v>
       </c>
       <c r="P3" t="n">
-        <v>440.5360565683129</v>
+        <v>440.8172976121525</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -7766,7 +7794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D231"/>
+  <dimension ref="A1:D232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12771,6 +12799,28 @@
         </is>
       </c>
     </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>-34.72456367329921,173.0924673411437</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>-34.72528923643388,173.09256978125202</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
